--- a/Testes/reescala/Teste populacao e gerações/Teste3/3_melhor_escala.xlsx
+++ b/Testes/reescala/Teste populacao e gerações/Teste3/3_melhor_escala.xlsx
@@ -2626,8 +2626,8 @@
       <c r="P19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" s="5" t="n">
-        <v>0</v>
+      <c r="Q19" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R19" s="5" t="n">
         <v>0</v>
@@ -3229,11 +3229,11 @@
       <c r="AF24" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AG24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" s="4" t="n">
-        <v>1</v>
+      <c r="AG24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH24" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AI24" s="5" t="n">
         <v>0</v>
@@ -3514,8 +3514,8 @@
       <c r="P27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>1</v>
+      <c r="Q27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R27" s="4" t="n">
         <v>1</v>
@@ -4561,11 +4561,11 @@
       <c r="AF36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AG36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH36" s="5" t="n">
-        <v>0</v>
+      <c r="AG36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AI36" s="5" t="n">
         <v>0</v>
